--- a/d/2026-07-18_会员有效性分析.xlsx
+++ b/d/2026-07-18_会员有效性分析.xlsx
@@ -6267,7 +6267,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -6290,7 +6290,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -6313,7 +6313,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13161289910</t>
+          <t>131****9910</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6336,7 +6336,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13293019486</t>
+          <t>132****9486</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6359,7 +6359,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13171607183</t>
+          <t>131****7183</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6382,7 +6382,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15701060983</t>
+          <t>157****0983</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6405,7 +6405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13911246265</t>
+          <t>139****6265</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6428,7 +6428,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18511946513</t>
+          <t>185****6513</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6451,7 +6451,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13272824691</t>
+          <t>132****4691</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6474,7 +6474,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13717972091</t>
+          <t>137****2091</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6497,7 +6497,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15201123395</t>
+          <t>152****3395</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6520,7 +6520,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15663258696</t>
+          <t>156****8696</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6543,7 +6543,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19814911319</t>
+          <t>198****1319</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6566,7 +6566,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17278102448</t>
+          <t>172****2448</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6589,7 +6589,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13521234380</t>
+          <t>135****4380</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6612,7 +6612,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18219829757</t>
+          <t>182****9757</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6635,7 +6635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17621765589</t>
+          <t>176****5589</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6658,7 +6658,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18611722515</t>
+          <t>186****2515</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6681,7 +6681,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13237413419</t>
+          <t>132****3419</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6704,7 +6704,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15891781131</t>
+          <t>158****1131</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6727,7 +6727,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13911290670</t>
+          <t>139****0670</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6750,7 +6750,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15227416428</t>
+          <t>152****6428</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6773,7 +6773,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15521301582</t>
+          <t>155****1582</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6796,7 +6796,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15733359639</t>
+          <t>157****9639</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6819,7 +6819,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13811162976</t>
+          <t>138****2976</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6842,7 +6842,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>18610932185</t>
+          <t>186****2185</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6865,7 +6865,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>18811031085</t>
+          <t>188****1085</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6888,7 +6888,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17883180691</t>
+          <t>178****0691</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6911,7 +6911,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>17368461289</t>
+          <t>173****1289</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6934,7 +6934,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17601663766</t>
+          <t>176****3766</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6957,7 +6957,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15397387154</t>
+          <t>153****7154</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6980,7 +6980,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>18333253777</t>
+          <t>183****3777</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -7003,7 +7003,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15811504668</t>
+          <t>158****4668</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -7026,7 +7026,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13269815521</t>
+          <t>132****5521</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -7049,7 +7049,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15378954286</t>
+          <t>153****4286</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -7072,7 +7072,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17821117333</t>
+          <t>178****7333</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -7095,7 +7095,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>18930090939</t>
+          <t>189****0939</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -7118,7 +7118,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15306893630</t>
+          <t>153****3630</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -7141,7 +7141,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13520701786</t>
+          <t>135****1786</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -7164,7 +7164,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15510720157</t>
+          <t>155****0157</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -7187,7 +7187,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17732888060</t>
+          <t>177****8060</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -7210,7 +7210,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13717797690</t>
+          <t>137****7690</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -7233,7 +7233,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13521788196</t>
+          <t>135****8196</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -7256,7 +7256,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>18010200217</t>
+          <t>180****0217</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7279,7 +7279,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15738922471</t>
+          <t>157****2471</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7302,7 +7302,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>17634516106</t>
+          <t>176****6106</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -7325,7 +7325,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13601173957</t>
+          <t>136****3957</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -7348,7 +7348,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17361368276</t>
+          <t>173****8276</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -7371,7 +7371,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>13720028581</t>
+          <t>137****8581</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -7394,7 +7394,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>13521708230</t>
+          <t>135****8230</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -7417,7 +7417,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17790714180</t>
+          <t>177****4180</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -7440,7 +7440,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18965088000</t>
+          <t>189****8000</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -7463,7 +7463,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13161940631</t>
+          <t>131****0631</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -7486,7 +7486,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15330073070</t>
+          <t>153****3070</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -7509,7 +7509,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13701026300</t>
+          <t>137****6300</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -7532,7 +7532,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18101894558</t>
+          <t>181****4558</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -7555,7 +7555,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15210286391</t>
+          <t>152****6391</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -7578,7 +7578,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>13811276310</t>
+          <t>138****6310</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -7601,7 +7601,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15045410228</t>
+          <t>150****0228</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -7624,7 +7624,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>15600257975</t>
+          <t>156****7975</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -7647,7 +7647,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>18618381620</t>
+          <t>186****1620</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -7670,7 +7670,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>13683369780</t>
+          <t>136****9780</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -7693,7 +7693,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17306918759</t>
+          <t>173****8759</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -7716,7 +7716,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>13030302041</t>
+          <t>130****2041</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -7739,7 +7739,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>13260013317</t>
+          <t>132****3317</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -7762,7 +7762,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>18710009180</t>
+          <t>187****9180</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -7785,7 +7785,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>18519083953</t>
+          <t>185****3953</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -7808,7 +7808,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>13818538850</t>
+          <t>138****8850</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -7831,7 +7831,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>13911248547</t>
+          <t>139****8547</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -7854,7 +7854,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>13331168893</t>
+          <t>133****8893</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -7877,7 +7877,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>15010512034</t>
+          <t>150****2034</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -7900,7 +7900,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>15161233164</t>
+          <t>151****3164</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -7923,7 +7923,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>13681499192</t>
+          <t>136****9192</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -7946,7 +7946,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>13611126869</t>
+          <t>136****6869</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -7969,7 +7969,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>15905889267</t>
+          <t>159****9267</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -7992,7 +7992,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>17778161185</t>
+          <t>177****1185</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -8015,7 +8015,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>18260924787</t>
+          <t>182****4787</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -8038,7 +8038,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>13808091475</t>
+          <t>138****1475</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -8061,7 +8061,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>13901281279</t>
+          <t>139****1279</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -8084,7 +8084,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>15311079792</t>
+          <t>153****9792</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -8107,7 +8107,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>19261039142</t>
+          <t>192****9142</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -8130,7 +8130,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>13810838107</t>
+          <t>138****8107</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -8153,7 +8153,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17710058506</t>
+          <t>177****8506</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -8176,7 +8176,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>17717810024</t>
+          <t>177****0024</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -8199,7 +8199,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>13910135667</t>
+          <t>139****5667</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -8222,7 +8222,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>13918718425</t>
+          <t>139****8425</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -8245,7 +8245,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>18111963268</t>
+          <t>181****3268</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -8268,7 +8268,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>13911622333</t>
+          <t>139****2333</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -8291,7 +8291,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>13616040095</t>
+          <t>136****0095</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -8314,7 +8314,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>17610855720</t>
+          <t>176****5720</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -8337,7 +8337,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>15566742107</t>
+          <t>155****2107</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -8360,7 +8360,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>18339470337</t>
+          <t>183****0337</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -8383,7 +8383,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13240108794</t>
+          <t>132****8794</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -8406,7 +8406,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13683024467</t>
+          <t>136****4467</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -8429,7 +8429,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>16632476171</t>
+          <t>166****6171</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -8452,7 +8452,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>13395905290</t>
+          <t>133****5290</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -8475,7 +8475,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13358299510</t>
+          <t>133****9510</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -8498,7 +8498,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18519663666</t>
+          <t>185****3666</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -8521,7 +8521,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>18001391086</t>
+          <t>180****1086</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -8544,7 +8544,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>18678155539</t>
+          <t>186****5539</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -8567,7 +8567,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>17605276848</t>
+          <t>176****6848</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -8590,7 +8590,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13120237385</t>
+          <t>131****7385</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -8613,7 +8613,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15531182175</t>
+          <t>155****2175</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -8636,7 +8636,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>18336002603</t>
+          <t>183****2603</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -8659,7 +8659,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>18210745020</t>
+          <t>182****5020</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -8682,7 +8682,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>17503270657</t>
+          <t>175****0657</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -8705,7 +8705,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>13381137800</t>
+          <t>133****7800</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -8728,7 +8728,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>13241952989</t>
+          <t>132****2989</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -8751,7 +8751,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>18111968858</t>
+          <t>181****8858</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -8774,7 +8774,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>13601208355</t>
+          <t>136****8355</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -8797,7 +8797,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>15601218618</t>
+          <t>156****8618</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -8820,7 +8820,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>15010269325</t>
+          <t>150****9325</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -8843,7 +8843,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>13705083183</t>
+          <t>137****3183</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -8866,7 +8866,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>13436441080</t>
+          <t>134****1080</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -8889,7 +8889,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>18385781992</t>
+          <t>183****1992</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -8912,7 +8912,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>15933476673</t>
+          <t>159****6673</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -8935,7 +8935,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>15754862672</t>
+          <t>157****2672</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -8958,7 +8958,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>13590149932</t>
+          <t>135****9932</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -8981,7 +8981,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>13681592680</t>
+          <t>136****2680</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -9004,7 +9004,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>15801252585</t>
+          <t>158****2585</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -9027,7 +9027,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>13552196092</t>
+          <t>135****6092</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -9050,7 +9050,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>13811874190</t>
+          <t>138****4190</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -9073,7 +9073,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>18682918886</t>
+          <t>186****8886</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -9096,7 +9096,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>18159967089</t>
+          <t>181****7089</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -9119,7 +9119,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>13261670129</t>
+          <t>132****0129</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -9142,7 +9142,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>18500798860</t>
+          <t>185****8860</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -9165,7 +9165,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>15732610800</t>
+          <t>157****0800</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -9188,7 +9188,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>13385309523</t>
+          <t>133****9523</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -9211,7 +9211,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>18633329155</t>
+          <t>186****9155</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -9234,7 +9234,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>18519660990</t>
+          <t>185****0990</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -9257,7 +9257,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>13301851456</t>
+          <t>133****1456</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -9280,7 +9280,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>18168578530</t>
+          <t>181****8530</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -9303,7 +9303,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>18500091875</t>
+          <t>185****1875</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -9326,7 +9326,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>15811249672</t>
+          <t>158****9672</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -9349,7 +9349,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>13681746167</t>
+          <t>136****6167</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -9372,7 +9372,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>18601950753</t>
+          <t>186****0753</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -9395,7 +9395,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>13122359792</t>
+          <t>131****9792</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -9418,7 +9418,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>13810575885</t>
+          <t>138****5885</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -9441,7 +9441,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>18911238350</t>
+          <t>189****8350</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -9464,7 +9464,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>13520836132</t>
+          <t>135****6132</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -9487,7 +9487,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>18817312560</t>
+          <t>188****2560</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -9510,7 +9510,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>18601249195</t>
+          <t>186****9195</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -9533,7 +9533,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>13761268200</t>
+          <t>137****8200</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -9556,7 +9556,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>18010058870</t>
+          <t>180****8870</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -9579,7 +9579,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>13701397707</t>
+          <t>137****7707</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -9602,7 +9602,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>13811027270</t>
+          <t>138****7270</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -9625,7 +9625,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>19107136807</t>
+          <t>191****6807</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -9648,7 +9648,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>18611820647</t>
+          <t>186****0647</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -9671,7 +9671,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>13001195866</t>
+          <t>130****5866</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -9694,7 +9694,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>15210414185</t>
+          <t>152****4185</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -9717,7 +9717,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>18811680651</t>
+          <t>188****0651</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -9740,7 +9740,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>18210232186</t>
+          <t>182****2186</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -9763,7 +9763,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>18210255124</t>
+          <t>182****5124</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -9786,7 +9786,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>13601188623</t>
+          <t>136****8623</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -9809,7 +9809,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>15373279618</t>
+          <t>153****9618</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -9832,7 +9832,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>18311095502</t>
+          <t>183****5502</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -9855,7 +9855,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>13311377412</t>
+          <t>133****7412</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -9878,7 +9878,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>13910242343</t>
+          <t>139****2343</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -9901,7 +9901,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>18910611506</t>
+          <t>189****1506</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -9924,7 +9924,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>18513106772</t>
+          <t>185****6772</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -9947,7 +9947,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>15175064705</t>
+          <t>151****4705</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -9970,7 +9970,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>18760005116</t>
+          <t>187****5116</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -9993,7 +9993,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>15827490045</t>
+          <t>158****0045</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -10016,7 +10016,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>13917486689</t>
+          <t>139****6689</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -10039,7 +10039,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>15010227544</t>
+          <t>150****7544</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -10062,7 +10062,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>13607587000</t>
+          <t>136****7000</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -10085,7 +10085,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>13166300779</t>
+          <t>131****0779</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -10108,7 +10108,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>13671927686</t>
+          <t>136****7686</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -10131,7 +10131,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>15321160352</t>
+          <t>153****0352</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -10154,7 +10154,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>18532310659</t>
+          <t>185****0659</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -10177,7 +10177,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>13693230356</t>
+          <t>136****0356</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -10200,7 +10200,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>15530315870</t>
+          <t>155****5870</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -10223,7 +10223,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>15300039878</t>
+          <t>153****9878</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -10246,7 +10246,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>15810955032</t>
+          <t>158****5032</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -10269,7 +10269,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>13146262311</t>
+          <t>131****2311</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -10292,7 +10292,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>13910762889</t>
+          <t>139****2889</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -10315,7 +10315,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>15011282507</t>
+          <t>150****2507</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -10338,7 +10338,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>13290625981</t>
+          <t>132****5981</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -10361,7 +10361,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>19932821118</t>
+          <t>199****1118</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -10384,7 +10384,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>13311279158</t>
+          <t>133****9158</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -10407,7 +10407,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>15195994197</t>
+          <t>151****4197</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -10430,7 +10430,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>18039040128</t>
+          <t>180****0128</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -10453,7 +10453,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>15545620971</t>
+          <t>155****0971</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -10476,7 +10476,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>13691576168</t>
+          <t>136****6168</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -10499,7 +10499,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>17759588798</t>
+          <t>177****8798</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -10522,7 +10522,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>18055131452</t>
+          <t>180****1452</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -10545,7 +10545,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>13910771770</t>
+          <t>139****1770</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -10568,7 +10568,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>13321180833</t>
+          <t>133****0833</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -10591,7 +10591,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>13488647740</t>
+          <t>134****7740</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -10614,7 +10614,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>18612596015</t>
+          <t>186****6015</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -10637,7 +10637,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>18301601370</t>
+          <t>183****1370</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -10660,7 +10660,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>13601206474</t>
+          <t>136****6474</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -10683,7 +10683,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>18860171876</t>
+          <t>188****1876</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -10706,7 +10706,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>13636631536</t>
+          <t>136****1536</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -10729,7 +10729,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>13683303927</t>
+          <t>136****3927</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -10752,7 +10752,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>15198805389</t>
+          <t>151****5389</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -10775,7 +10775,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>17359032093</t>
+          <t>173****2093</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -10798,7 +10798,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>13681483984</t>
+          <t>136****3984</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -10821,7 +10821,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>18501369159</t>
+          <t>185****9159</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -10844,7 +10844,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>17380008867</t>
+          <t>173****8867</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -10867,7 +10867,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>15201352750</t>
+          <t>152****2750</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -10890,7 +10890,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>13488619695</t>
+          <t>134****9695</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -10913,7 +10913,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>18220538460</t>
+          <t>182****8460</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -10936,7 +10936,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>15295165686</t>
+          <t>152****5686</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -10959,7 +10959,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>13466605322</t>
+          <t>134****5322</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -10982,7 +10982,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>13331991773</t>
+          <t>133****1773</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -11005,7 +11005,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>18311484501</t>
+          <t>183****4501</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -11028,7 +11028,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>13581501297</t>
+          <t>135****1297</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -11051,7 +11051,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>15311196683</t>
+          <t>153****6683</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -11074,7 +11074,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>18001911598</t>
+          <t>180****1598</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -11097,7 +11097,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>15910355812</t>
+          <t>159****5812</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -11120,7 +11120,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>13913933990</t>
+          <t>139****3990</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -11143,7 +11143,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>13910381032</t>
+          <t>139****1032</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -11166,7 +11166,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>15081204266</t>
+          <t>150****4266</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -11189,7 +11189,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>18116660220</t>
+          <t>181****0220</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -11212,7 +11212,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>13716008576</t>
+          <t>137****8576</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -11235,7 +11235,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>13911888618</t>
+          <t>139****8618</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -11258,7 +11258,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>15759221390</t>
+          <t>157****1390</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -11281,7 +11281,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>13753569783</t>
+          <t>137****9783</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -11304,7 +11304,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>18613879907</t>
+          <t>186****9907</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -11327,7 +11327,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>13764294612</t>
+          <t>137****4612</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -11350,7 +11350,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>15827101791</t>
+          <t>158****1791</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -11373,7 +11373,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>13269486610</t>
+          <t>132****6610</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -11396,7 +11396,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>13321178267</t>
+          <t>133****8267</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -11419,7 +11419,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>18310997088</t>
+          <t>183****7088</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -11442,7 +11442,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>15811336178</t>
+          <t>158****6178</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -11465,7 +11465,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>13701969018</t>
+          <t>137****9018</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -11488,7 +11488,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>15718895426</t>
+          <t>157****5426</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -11511,7 +11511,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>13911860509</t>
+          <t>139****0509</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -11534,7 +11534,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>18018519252</t>
+          <t>180****9252</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -11557,7 +11557,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>13810586912</t>
+          <t>138****6912</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -11580,7 +11580,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>13910903939</t>
+          <t>139****3939</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -11603,7 +11603,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>18611734699</t>
+          <t>186****4699</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -11626,7 +11626,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>15201447010</t>
+          <t>152****7010</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -11649,7 +11649,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>18905929861</t>
+          <t>189****9861</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -11672,7 +11672,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>13718700892</t>
+          <t>137****0892</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -11695,7 +11695,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>18616502346</t>
+          <t>186****2346</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -11718,7 +11718,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>18612939929</t>
+          <t>186****9929</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -11741,7 +11741,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>18262299666</t>
+          <t>182****9666</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -11764,7 +11764,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>18439401112</t>
+          <t>184****1112</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -11787,7 +11787,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>13811316899</t>
+          <t>138****6899</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -11810,7 +11810,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>13905910511</t>
+          <t>139****0511</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -11833,7 +11833,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>13911751260</t>
+          <t>139****1260</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -11856,7 +11856,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>15116938941</t>
+          <t>151****8941</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -11879,7 +11879,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>18803141991</t>
+          <t>188****1991</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -11902,7 +11902,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>13521172823</t>
+          <t>135****2823</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -11925,7 +11925,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>13008080555</t>
+          <t>130****0555</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -11948,7 +11948,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>13810429143</t>
+          <t>138****9143</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -11971,7 +11971,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>15821145415</t>
+          <t>158****5415</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -11994,7 +11994,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>18610099262</t>
+          <t>186****9262</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -12017,7 +12017,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>18088286821</t>
+          <t>180****6821</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -12040,7 +12040,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>13391528767</t>
+          <t>133****8767</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -12063,7 +12063,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>15305475924</t>
+          <t>153****5924</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -12086,7 +12086,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>15300325001</t>
+          <t>153****5001</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -12109,7 +12109,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>15600233213</t>
+          <t>156****3213</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -12132,7 +12132,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>19828386370</t>
+          <t>198****6370</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -12155,7 +12155,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>15810190917</t>
+          <t>158****0917</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -12178,7 +12178,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>17630974613</t>
+          <t>176****4613</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -12201,7 +12201,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>13911918137</t>
+          <t>139****8137</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -12224,7 +12224,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>13811728032</t>
+          <t>138****8032</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -12247,7 +12247,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>15618709987</t>
+          <t>156****9987</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -12270,7 +12270,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>18332082244</t>
+          <t>183****2244</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -12293,7 +12293,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>18910373510</t>
+          <t>189****3510</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -12316,7 +12316,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>13701028544</t>
+          <t>137****8544</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -12339,7 +12339,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>16630799321</t>
+          <t>166****9321</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -12362,7 +12362,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>15300636118</t>
+          <t>153****6118</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -12385,7 +12385,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>17601273516</t>
+          <t>176****3516</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -12408,7 +12408,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>18301163023</t>
+          <t>183****3023</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -12431,7 +12431,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>13665252313</t>
+          <t>136****2313</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -12454,7 +12454,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>18510008593</t>
+          <t>185****8593</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -12477,7 +12477,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>13959152114</t>
+          <t>139****2114</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -12500,7 +12500,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>16604148777</t>
+          <t>166****8777</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -12523,7 +12523,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>17301121619</t>
+          <t>173****1619</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -12546,7 +12546,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>13079611389</t>
+          <t>130****1389</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -12569,7 +12569,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>13671897012</t>
+          <t>136****7012</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -12592,7 +12592,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>18152584730</t>
+          <t>181****4730</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -12615,7 +12615,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>15048686819</t>
+          <t>150****6819</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -12638,7 +12638,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>13810206422</t>
+          <t>138****6422</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -12661,7 +12661,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>13581688824</t>
+          <t>135****8824</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -12684,7 +12684,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>13910389889</t>
+          <t>139****9889</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -12707,7 +12707,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>18120234785</t>
+          <t>181****4785</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -12730,7 +12730,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>18210641792</t>
+          <t>182****1792</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -12753,7 +12753,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>18612798646</t>
+          <t>186****8646</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -12776,7 +12776,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>13029570628</t>
+          <t>130****0628</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -12799,7 +12799,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>13817928936</t>
+          <t>138****8936</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -12822,7 +12822,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>13522251340</t>
+          <t>135****1340</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -12845,7 +12845,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>17310230575</t>
+          <t>173****0575</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -12868,7 +12868,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>13755325947</t>
+          <t>137****5947</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -12891,7 +12891,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>13261857667</t>
+          <t>132****7667</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -12914,7 +12914,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>15809317030</t>
+          <t>158****7030</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -12937,7 +12937,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>18239463963</t>
+          <t>182****3963</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -12960,7 +12960,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>18721970468</t>
+          <t>187****0468</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -12983,7 +12983,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>17702295481</t>
+          <t>177****5481</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -13006,7 +13006,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>18917385750</t>
+          <t>189****5750</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -13029,7 +13029,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>15600284358</t>
+          <t>156****4358</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -13052,7 +13052,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>18201157053</t>
+          <t>182****7053</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -13075,7 +13075,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>13810402021</t>
+          <t>138****2021</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -13098,7 +13098,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>13716243870</t>
+          <t>137****3870</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -13121,7 +13121,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>13718093269</t>
+          <t>137****3269</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -13144,7 +13144,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>13641251349</t>
+          <t>136****1349</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -13167,7 +13167,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>13911397295</t>
+          <t>139****7295</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -13190,7 +13190,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>17778169607</t>
+          <t>177****9607</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -13213,7 +13213,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>13681998096</t>
+          <t>136****8096</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -13236,7 +13236,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>18210230765</t>
+          <t>182****0765</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -13259,7 +13259,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>13699270194</t>
+          <t>136****0194</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13811162976</t>
+          <t>138****2976</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13911290670</t>
+          <t>139****0670</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17732888060</t>
+          <t>177****8060</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13552196092</t>
+          <t>135****6092</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18513106772</t>
+          <t>185****6772</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13520836132</t>
+          <t>135****6132</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13911397295</t>
+          <t>139****7295</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -13575,7 +13575,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13269486610</t>
+          <t>132****6610</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -13627,7 +13627,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13641251349</t>
+          <t>136****1349</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15663258696</t>
+          <t>156****8696</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15378954286</t>
+          <t>153****4286</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13521788196</t>
+          <t>135****8196</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15330073070</t>
+          <t>153****3070</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17610855720</t>
+          <t>176****5720</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15210286391</t>
+          <t>152****6391</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15210414185</t>
+          <t>152****4185</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18210745020</t>
+          <t>182****5020</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17503270657</t>
+          <t>175****0657</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18613879907</t>
+          <t>186****9907</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13079611389</t>
+          <t>130****1389</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13681592680</t>
+          <t>136****2680</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15011282507</t>
+          <t>150****2507</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15801252585</t>
+          <t>158****2585</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13811874190</t>
+          <t>138****4190</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13810586912</t>
+          <t>138****6912</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>18239463963</t>
+          <t>182****3963</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>13810429143</t>
+          <t>138****9143</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15010227544</t>
+          <t>150****7544</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13293019486</t>
+          <t>132****9486</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15701060983</t>
+          <t>157****0983</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13521234380</t>
+          <t>135****4380</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15227416428</t>
+          <t>152****6428</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -14381,7 +14381,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17361368276</t>
+          <t>173****8276</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>15905889267</t>
+          <t>159****9267</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13260013317</t>
+          <t>132****3317</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -14459,7 +14459,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>17778161185</t>
+          <t>177****1185</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15809317030</t>
+          <t>158****7030</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>18439401112</t>
+          <t>184****1112</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13466605322</t>
+          <t>134****5322</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>13601208355</t>
+          <t>136****8355</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15373279618</t>
+          <t>153****9618</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13716243870</t>
+          <t>137****3870</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>18501369159</t>
+          <t>185****9159</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>18055131452</t>
+          <t>180****1452</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13581688824</t>
+          <t>135****8824</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>18333253777</t>
+          <t>183****3777</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15081204266</t>
+          <t>150****4266</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -14797,7 +14797,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>18168578530</t>
+          <t>181****8530</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>18601249195</t>
+          <t>186****9195</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>13810206422</t>
+          <t>138****6422</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>13029570628</t>
+          <t>130****0628</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>13240108794</t>
+          <t>132****8794</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -14979,7 +14979,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>15116938941</t>
+          <t>151****8941</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>18500091875</t>
+          <t>185****1875</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13910771770</t>
+          <t>139****1770</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>18039040128</t>
+          <t>180****0128</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -15161,7 +15161,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>13811027270</t>
+          <t>138****7270</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -15239,7 +15239,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>13911622333</t>
+          <t>139****2333</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>18710009180</t>
+          <t>187****9180</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>15600233213</t>
+          <t>156****3213</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -15343,7 +15343,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>13171607183</t>
+          <t>131****7183</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>17710058506</t>
+          <t>177****8506</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -15395,7 +15395,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15010269325</t>
+          <t>150****9325</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>17883180691</t>
+          <t>178****0691</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>13808091475</t>
+          <t>138****1475</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -15525,7 +15525,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>18917385750</t>
+          <t>189****5750</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>15618709987</t>
+          <t>156****9987</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>18510008593</t>
+          <t>185****8593</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>13764294612</t>
+          <t>137****4612</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>18001911598</t>
+          <t>180****1598</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13161289910</t>
+          <t>131****9910</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>17790714180</t>
+          <t>177****4180</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>15300325001</t>
+          <t>153****5001</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>13601188623</t>
+          <t>136****8623</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13918718425</t>
+          <t>139****8425</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>13301851456</t>
+          <t>133****1456</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>18817312560</t>
+          <t>188****2560</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>18678155539</t>
+          <t>186****5539</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>13681998096</t>
+          <t>136****8096</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>18220538460</t>
+          <t>182****8460</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>15891781131</t>
+          <t>158****1131</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -16149,7 +16149,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>15733359639</t>
+          <t>157****9639</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -16175,7 +16175,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -16253,7 +16253,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>13331168893</t>
+          <t>133****8893</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>13001195866</t>
+          <t>130****5866</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>15718895426</t>
+          <t>157****5426</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>15045410228</t>
+          <t>150****0228</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>13391528767</t>
+          <t>133****8767</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>13029570628</t>
+          <t>130****0628</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>13910762889</t>
+          <t>139****2889</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>13811728032</t>
+          <t>138****8032</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>13910242343</t>
+          <t>139****2343</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>13241952989</t>
+          <t>132****2989</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -16565,7 +16565,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>18610932185</t>
+          <t>186****2185</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>13030302041</t>
+          <t>130****2041</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -16643,7 +16643,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13665252313</t>
+          <t>136****2313</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>18910611506</t>
+          <t>189****1506</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>15201352750</t>
+          <t>152****2750</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>18611820647</t>
+          <t>186****0647</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>13761268200</t>
+          <t>137****8200</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -16825,7 +16825,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>15821145415</t>
+          <t>158****5415</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>13521172823</t>
+          <t>135****2823</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>18010058870</t>
+          <t>180****8870</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>18152584730</t>
+          <t>181****4730</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>13911246265</t>
+          <t>139****6265</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>13701026300</t>
+          <t>137****6300</t>
         </is>
       </c>
       <c r="E146" t="n">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>13913933990</t>
+          <t>139****3990</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -17137,7 +17137,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>15754862672</t>
+          <t>157****2672</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E149" t="n">
@@ -17189,7 +17189,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -17215,7 +17215,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>13683369780</t>
+          <t>136****9780</t>
         </is>
       </c>
       <c r="E151" t="n">
@@ -17241,7 +17241,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>13311377412</t>
+          <t>133****7412</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>15601218618</t>
+          <t>156****8618</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>13910135667</t>
+          <t>139****5667</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>13607587000</t>
+          <t>136****7000</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -17423,7 +17423,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -17475,7 +17475,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>18811031085</t>
+          <t>188****1085</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18018519252</t>
+          <t>180****9252</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -17527,7 +17527,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>16630799321</t>
+          <t>166****9321</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>13720028581</t>
+          <t>137****8581</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -17579,7 +17579,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>15521301582</t>
+          <t>155****1582</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>13321180833</t>
+          <t>133****0833</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>13581501297</t>
+          <t>135****1297</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>15311196683</t>
+          <t>153****6683</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>13683303927</t>
+          <t>136****3927</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -17761,7 +17761,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>18811680651</t>
+          <t>188****0651</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>17778169607</t>
+          <t>177****9607</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>13008080555</t>
+          <t>130****0555</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -17865,7 +17865,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>18682918886</t>
+          <t>186****8886</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>17601663766</t>
+          <t>176****3766</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -17943,7 +17943,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>13681499192</t>
+          <t>136****9192</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>15198805389</t>
+          <t>151****5389</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>17630974613</t>
+          <t>176****4613</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -18047,7 +18047,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>13681483984</t>
+          <t>136****3984</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>15161233164</t>
+          <t>151****3164</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>13611126869</t>
+          <t>136****6869</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>18201157053</t>
+          <t>182****7053</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>18210255124</t>
+          <t>182****5124</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>15321160352</t>
+          <t>153****0352</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -18255,7 +18255,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>18611734699</t>
+          <t>186****4699</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>17605276848</t>
+          <t>176****6848</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>13488619695</t>
+          <t>134****9695</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>13717972091</t>
+          <t>137****2091</t>
         </is>
       </c>
       <c r="E194" t="n">
@@ -18359,7 +18359,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -18385,7 +18385,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>13269815521</t>
+          <t>132****5521</t>
         </is>
       </c>
       <c r="E196" t="n">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>13810838107</t>
+          <t>138****8107</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>13811316899</t>
+          <t>138****6899</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>13910903939</t>
+          <t>139****3939</t>
         </is>
       </c>
       <c r="E199" t="n">
@@ -18489,7 +18489,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>18500798860</t>
+          <t>185****8860</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -18541,7 +18541,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>18332082244</t>
+          <t>183****2244</t>
         </is>
       </c>
       <c r="E202" t="n">
@@ -18567,7 +18567,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>15201447010</t>
+          <t>152****7010</t>
         </is>
       </c>
       <c r="E203" t="n">
@@ -18593,7 +18593,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>18610099262</t>
+          <t>186****9262</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>19107136807</t>
+          <t>191****6807</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -18645,7 +18645,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>18116660220</t>
+          <t>181****0220</t>
         </is>
       </c>
       <c r="E208" t="n">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>19828386370</t>
+          <t>198****6370</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -18775,7 +18775,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -18827,7 +18827,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>15306893630</t>
+          <t>153****3630</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>15810190917</t>
+          <t>158****0917</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -18879,7 +18879,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>13911751260</t>
+          <t>139****1260</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>18311484501</t>
+          <t>183****4501</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>18088286821</t>
+          <t>180****6821</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>15175064705</t>
+          <t>151****4705</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>13331168893</t>
+          <t>133****8893</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -19009,7 +19009,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>18219829757</t>
+          <t>182****9757</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -19061,7 +19061,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>15195994197</t>
+          <t>151****4197</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -19087,7 +19087,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>13911248547</t>
+          <t>139****8547</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>18519083953</t>
+          <t>185****3953</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -19165,7 +19165,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E226" t="n">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>13290625981</t>
+          <t>132****5981</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -19217,7 +19217,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>18803141991</t>
+          <t>188****1991</t>
         </is>
       </c>
       <c r="E228" t="n">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E229" t="n">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>13601173957</t>
+          <t>136****3957</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>15811249672</t>
+          <t>158****9672</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>15732610800</t>
+          <t>157****0800</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>13601206474</t>
+          <t>136****6474</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>13910389889</t>
+          <t>139****9889</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -19399,7 +19399,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>18301163023</t>
+          <t>183****3023</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>13311279158</t>
+          <t>133****9158</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>18210230765</t>
+          <t>182****0765</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>13699270194</t>
+          <t>136****0194</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -19529,7 +19529,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>18262299666</t>
+          <t>182****9666</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>15759221390</t>
+          <t>157****1390</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>13753569783</t>
+          <t>137****9783</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>17359032093</t>
+          <t>173****2093</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -19685,7 +19685,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>18965088000</t>
+          <t>189****8000</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -19711,7 +19711,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>18159967089</t>
+          <t>181****7089</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -19763,7 +19763,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -19815,7 +19815,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -19867,7 +19867,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>15510720157</t>
+          <t>155****0157</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>18519663666</t>
+          <t>185****3666</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>13522251340</t>
+          <t>135****1340</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>18010200217</t>
+          <t>180****0217</t>
         </is>
       </c>
       <c r="E256" t="n">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>15305475924</t>
+          <t>153****5924</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -19997,7 +19997,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -20023,7 +20023,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>13717797690</t>
+          <t>137****7690</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>13161940631</t>
+          <t>131****0631</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>18519660990</t>
+          <t>185****0990</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E262" t="n">
@@ -20127,7 +20127,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>19261039142</t>
+          <t>192****9142</t>
         </is>
       </c>
       <c r="E263" t="n">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>18120234785</t>
+          <t>181****4785</t>
         </is>
       </c>
       <c r="E264" t="n">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>18311095502</t>
+          <t>183****5502</t>
         </is>
       </c>
       <c r="E265" t="n">
@@ -20205,7 +20205,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>13436441080</t>
+          <t>134****1080</t>
         </is>
       </c>
       <c r="E266" t="n">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>13261670129</t>
+          <t>132****0129</t>
         </is>
       </c>
       <c r="E267" t="n">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>18010200217</t>
+          <t>180****0217</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>18612596015</t>
+          <t>186****6015</t>
         </is>
       </c>
       <c r="E269" t="n">
@@ -20309,7 +20309,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>15305475924</t>
+          <t>153****5924</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -20335,7 +20335,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -20361,7 +20361,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>18930090939</t>
+          <t>189****0939</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -20387,7 +20387,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -20413,7 +20413,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>18616502346</t>
+          <t>186****2346</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>13681746167</t>
+          <t>136****6167</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>13671897012</t>
+          <t>136****7012</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>17380008867</t>
+          <t>173****8867</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -20517,7 +20517,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>13917486689</t>
+          <t>139****6689</t>
         </is>
       </c>
       <c r="E278" t="n">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>13911918137</t>
+          <t>139****8137</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>15010512034</t>
+          <t>150****2034</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -20673,7 +20673,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>16604148777</t>
+          <t>166****8777</t>
         </is>
       </c>
       <c r="E284" t="n">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>15827101791</t>
+          <t>158****1791</t>
         </is>
       </c>
       <c r="E285" t="n">
@@ -20725,7 +20725,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>13321178267</t>
+          <t>133****8267</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>15811336178</t>
+          <t>158****6178</t>
         </is>
       </c>
       <c r="E287" t="n">
@@ -20777,7 +20777,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E288" t="n">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>18860171876</t>
+          <t>188****1876</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>13705083183</t>
+          <t>137****3183</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>15827490045</t>
+          <t>158****0045</t>
         </is>
       </c>
       <c r="E291" t="n">
@@ -20881,7 +20881,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>13755325947</t>
+          <t>137****5947</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -20907,7 +20907,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -20985,7 +20985,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>18001391086</t>
+          <t>180****1086</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -21037,7 +21037,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>18532310659</t>
+          <t>185****0659</t>
         </is>
       </c>
       <c r="E298" t="n">
@@ -21063,7 +21063,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>13718700892</t>
+          <t>137****0892</t>
         </is>
       </c>
       <c r="E299" t="n">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E300" t="n">
@@ -21115,7 +21115,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>18618381620</t>
+          <t>186****1620</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -21141,7 +21141,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>13691576168</t>
+          <t>136****6168</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>13120237385</t>
+          <t>131****7385</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>13381137800</t>
+          <t>133****7800</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>13641251349</t>
+          <t>136****1349</t>
         </is>
       </c>
       <c r="E305" t="n">
@@ -21245,7 +21245,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -21271,7 +21271,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>13905910511</t>
+          <t>139****0511</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -21323,7 +21323,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E309" t="n">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>13701397707</t>
+          <t>137****7707</t>
         </is>
       </c>
       <c r="E310" t="n">
@@ -21375,7 +21375,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>15300039878</t>
+          <t>153****9878</t>
         </is>
       </c>
       <c r="E311" t="n">
@@ -21401,7 +21401,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -21427,7 +21427,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>17278102448</t>
+          <t>172****2448</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>15738922471</t>
+          <t>157****2471</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -21505,7 +21505,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>17601273516</t>
+          <t>176****3516</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>13911860509</t>
+          <t>139****0509</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -21557,7 +21557,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>18905929861</t>
+          <t>189****9861</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -21609,7 +21609,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>15910355812</t>
+          <t>159****5812</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>18210641792</t>
+          <t>182****1792</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>18911238350</t>
+          <t>189****8350</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -21713,7 +21713,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -21739,7 +21739,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>19932821118</t>
+          <t>199****1118</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -21765,7 +21765,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -21817,7 +21817,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E329" t="n">
@@ -21869,7 +21869,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>13331991773</t>
+          <t>133****1773</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>13817928936</t>
+          <t>138****8936</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -21921,7 +21921,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -21999,7 +21999,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>13616040095</t>
+          <t>136****0095</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -22051,7 +22051,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>13636631536</t>
+          <t>136****1536</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E338" t="n">
@@ -22103,7 +22103,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>13146262311</t>
+          <t>131****2311</t>
         </is>
       </c>
       <c r="E339" t="n">
@@ -22129,7 +22129,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>15201123395</t>
+          <t>152****3395</t>
         </is>
       </c>
       <c r="E340" t="n">
@@ -22155,7 +22155,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>13521708230</t>
+          <t>135****8230</t>
         </is>
       </c>
       <c r="E341" t="n">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E342" t="n">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>15718895426</t>
+          <t>157****5426</t>
         </is>
       </c>
       <c r="E343" t="n">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E344" t="n">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>17717810024</t>
+          <t>177****0024</t>
         </is>
       </c>
       <c r="E345" t="n">
@@ -22285,7 +22285,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E346" t="n">
@@ -22311,7 +22311,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E347" t="n">
@@ -22337,7 +22337,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>18336002603</t>
+          <t>183****2603</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E349" t="n">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>13395905290</t>
+          <t>133****5290</t>
         </is>
       </c>
       <c r="E351" t="n">
@@ -22441,7 +22441,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E352" t="n">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>18760005116</t>
+          <t>187****5116</t>
         </is>
       </c>
       <c r="E353" t="n">
@@ -22493,7 +22493,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>15600257975</t>
+          <t>156****7975</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -22545,7 +22545,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>13683024467</t>
+          <t>136****4467</t>
         </is>
       </c>
       <c r="E356" t="n">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>13237413419</t>
+          <t>132****3419</t>
         </is>
       </c>
       <c r="E357" t="n">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>13901281279</t>
+          <t>139****1279</t>
         </is>
       </c>
       <c r="E358" t="n">
@@ -22623,7 +22623,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>18601950753</t>
+          <t>186****0753</t>
         </is>
       </c>
       <c r="E359" t="n">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E360" t="n">
@@ -22675,7 +22675,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E362" t="n">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E363" t="n">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>13358299510</t>
+          <t>133****9510</t>
         </is>
       </c>
       <c r="E364" t="n">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>18965088000</t>
+          <t>189****8000</t>
         </is>
       </c>
       <c r="E365" t="n">
@@ -22805,7 +22805,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E366" t="n">
@@ -22831,7 +22831,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>17821117333</t>
+          <t>178****7333</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -22857,7 +22857,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>13590149932</t>
+          <t>135****9932</t>
         </is>
       </c>
       <c r="E368" t="n">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E369" t="n">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>15295165686</t>
+          <t>152****5686</t>
         </is>
       </c>
       <c r="E370" t="n">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>13272824691</t>
+          <t>132****4691</t>
         </is>
       </c>
       <c r="E371" t="n">
@@ -22961,7 +22961,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>18260924787</t>
+          <t>182****4787</t>
         </is>
       </c>
       <c r="E372" t="n">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E373" t="n">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>18612939929</t>
+          <t>186****9929</t>
         </is>
       </c>
       <c r="E374" t="n">
@@ -23039,7 +23039,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>15600284358</t>
+          <t>156****4358</t>
         </is>
       </c>
       <c r="E375" t="n">
@@ -23065,7 +23065,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>13716008576</t>
+          <t>137****8576</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>18301601370</t>
+          <t>183****1370</t>
         </is>
       </c>
       <c r="E377" t="n">
@@ -23117,7 +23117,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E378" t="n">
@@ -23143,7 +23143,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E379" t="n">
@@ -23169,7 +23169,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -23195,7 +23195,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E381" t="n">
@@ -23221,7 +23221,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E382" t="n">
@@ -23247,7 +23247,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>13910381032</t>
+          <t>139****1032</t>
         </is>
       </c>
       <c r="E383" t="n">
@@ -23273,7 +23273,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>19814911319</t>
+          <t>198****1319</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>13520701786</t>
+          <t>135****1786</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -23325,7 +23325,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -23351,7 +23351,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>15933476673</t>
+          <t>159****6673</t>
         </is>
       </c>
       <c r="E387" t="n">
@@ -23377,7 +23377,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E388" t="n">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E389" t="n">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>15311079792</t>
+          <t>153****9792</t>
         </is>
       </c>
       <c r="E390" t="n">
@@ -23455,7 +23455,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E391" t="n">
@@ -23481,7 +23481,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>13718093269</t>
+          <t>137****3269</t>
         </is>
       </c>
       <c r="E392" t="n">
@@ -23507,7 +23507,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>16632476171</t>
+          <t>166****6171</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -23533,7 +23533,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>13911860509</t>
+          <t>139****0509</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E395" t="n">
@@ -23585,7 +23585,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>13810402021</t>
+          <t>138****2021</t>
         </is>
       </c>
       <c r="E396" t="n">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E397" t="n">
@@ -23637,7 +23637,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>18111963268</t>
+          <t>181****3268</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -23663,7 +23663,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E400" t="n">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>18339470337</t>
+          <t>183****0337</t>
         </is>
       </c>
       <c r="E401" t="n">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>13683303927</t>
+          <t>136****3927</t>
         </is>
       </c>
       <c r="E402" t="n">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E403" t="n">
@@ -23793,7 +23793,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E404" t="n">
@@ -23819,7 +23819,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>13720028581</t>
+          <t>137****8581</t>
         </is>
       </c>
       <c r="E405" t="n">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -23871,7 +23871,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -23897,7 +23897,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E408" t="n">
@@ -23923,7 +23923,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E409" t="n">
@@ -23949,7 +23949,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>13261857667</t>
+          <t>132****7667</t>
         </is>
       </c>
       <c r="E410" t="n">
@@ -23975,7 +23975,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>13910389889</t>
+          <t>139****9889</t>
         </is>
       </c>
       <c r="E411" t="n">
@@ -24001,7 +24001,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -24027,7 +24027,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E413" t="n">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E414" t="n">
@@ -24079,7 +24079,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>13911888618</t>
+          <t>139****8618</t>
         </is>
       </c>
       <c r="E415" t="n">
@@ -24105,7 +24105,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>13488647740</t>
+          <t>134****7740</t>
         </is>
       </c>
       <c r="E416" t="n">
@@ -24131,7 +24131,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>17368461289</t>
+          <t>173****1289</t>
         </is>
       </c>
       <c r="E417" t="n">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>17634516106</t>
+          <t>176****6106</t>
         </is>
       </c>
       <c r="E418" t="n">
@@ -24183,7 +24183,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E419" t="n">
@@ -24209,7 +24209,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E420" t="n">
@@ -24235,7 +24235,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>15397387154</t>
+          <t>153****7154</t>
         </is>
       </c>
       <c r="E421" t="n">
@@ -24261,7 +24261,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E422" t="n">
@@ -24287,7 +24287,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E423" t="n">
@@ -24313,7 +24313,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>18511946513</t>
+          <t>185****6513</t>
         </is>
       </c>
       <c r="E424" t="n">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E425" t="n">
@@ -24365,7 +24365,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>15811504668</t>
+          <t>158****4668</t>
         </is>
       </c>
       <c r="E426" t="n">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E427" t="n">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E428" t="n">
@@ -24443,7 +24443,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E429" t="n">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>18210232186</t>
+          <t>182****2186</t>
         </is>
       </c>
       <c r="E430" t="n">
@@ -24495,7 +24495,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>15566742107</t>
+          <t>155****2107</t>
         </is>
       </c>
       <c r="E431" t="n">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -24547,7 +24547,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>15545620971</t>
+          <t>155****0971</t>
         </is>
       </c>
       <c r="E433" t="n">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>18385781992</t>
+          <t>183****1992</t>
         </is>
       </c>
       <c r="E434" t="n">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>13810575885</t>
+          <t>138****5885</t>
         </is>
       </c>
       <c r="E435" t="n">
@@ -24625,7 +24625,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>15531182175</t>
+          <t>155****2175</t>
         </is>
       </c>
       <c r="E436" t="n">
@@ -24651,7 +24651,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E437" t="n">
@@ -24677,7 +24677,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E438" t="n">
@@ -24703,7 +24703,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>13701028544</t>
+          <t>137****8544</t>
         </is>
       </c>
       <c r="E439" t="n">
@@ -24729,7 +24729,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E441" t="n">
@@ -24781,7 +24781,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E442" t="n">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E443" t="n">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>13818538850</t>
+          <t>138****8850</t>
         </is>
       </c>
       <c r="E444" t="n">
@@ -24859,7 +24859,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>18721970468</t>
+          <t>187****0468</t>
         </is>
       </c>
       <c r="E445" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E446" t="n">
@@ -24911,7 +24911,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>18611722515</t>
+          <t>186****2515</t>
         </is>
       </c>
       <c r="E447" t="n">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E448" t="n">
@@ -24963,7 +24963,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>18101894558</t>
+          <t>181****4558</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>13701969018</t>
+          <t>137****9018</t>
         </is>
       </c>
       <c r="E450" t="n">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>13811276310</t>
+          <t>138****6310</t>
         </is>
       </c>
       <c r="E451" t="n">
@@ -25041,7 +25041,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E452" t="n">
@@ -25067,7 +25067,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E453" t="n">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>17759588798</t>
+          <t>177****8798</t>
         </is>
       </c>
       <c r="E454" t="n">
@@ -25119,7 +25119,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E455" t="n">
@@ -25145,7 +25145,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E456" t="n">
@@ -25171,7 +25171,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>17702295481</t>
+          <t>177****5481</t>
         </is>
       </c>
       <c r="E457" t="n">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>17621765589</t>
+          <t>176****5589</t>
         </is>
       </c>
       <c r="E458" t="n">
@@ -25223,7 +25223,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E459" t="n">
@@ -25249,7 +25249,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>15810955032</t>
+          <t>158****5032</t>
         </is>
       </c>
       <c r="E460" t="n">
@@ -25275,7 +25275,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>18612798646</t>
+          <t>186****8646</t>
         </is>
       </c>
       <c r="E461" t="n">
@@ -25301,7 +25301,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>19932821118</t>
+          <t>199****1118</t>
         </is>
       </c>
       <c r="E462" t="n">
@@ -25327,7 +25327,7 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E463" t="n">
@@ -25353,7 +25353,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>17310230575</t>
+          <t>173****0575</t>
         </is>
       </c>
       <c r="E464" t="n">
@@ -25379,7 +25379,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>15530315870</t>
+          <t>155****5870</t>
         </is>
       </c>
       <c r="E465" t="n">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E466" t="n">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E467" t="n">
@@ -25457,7 +25457,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E468" t="n">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>17301121619</t>
+          <t>173****1619</t>
         </is>
       </c>
       <c r="E469" t="n">
@@ -25509,7 +25509,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E470" t="n">
@@ -25535,7 +25535,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>18633329155</t>
+          <t>186****9155</t>
         </is>
       </c>
       <c r="E471" t="n">
@@ -25561,7 +25561,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E472" t="n">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>15510720157</t>
+          <t>155****0157</t>
         </is>
       </c>
       <c r="E473" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>15048686819</t>
+          <t>150****6819</t>
         </is>
       </c>
       <c r="E474" t="n">
@@ -25639,7 +25639,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>18910373510</t>
+          <t>189****3510</t>
         </is>
       </c>
       <c r="E475" t="n">
@@ -25665,7 +25665,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E476" t="n">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>18310997088</t>
+          <t>183****7088</t>
         </is>
       </c>
       <c r="E477" t="n">
@@ -25717,7 +25717,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E478" t="n">
@@ -25743,7 +25743,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>18111968858</t>
+          <t>181****8858</t>
         </is>
       </c>
       <c r="E479" t="n">
@@ -25769,7 +25769,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E480" t="n">
@@ -25795,7 +25795,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E481" t="n">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>15311079792</t>
+          <t>153****9792</t>
         </is>
       </c>
       <c r="E482" t="n">
@@ -25847,7 +25847,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>13166300779</t>
+          <t>131****0779</t>
         </is>
       </c>
       <c r="E483" t="n">
@@ -25873,7 +25873,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -25899,7 +25899,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>13717972091</t>
+          <t>137****2091</t>
         </is>
       </c>
       <c r="E485" t="n">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E486" t="n">
@@ -25951,7 +25951,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>13910135667</t>
+          <t>139****5667</t>
         </is>
       </c>
       <c r="E487" t="n">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E488" t="n">
@@ -26003,7 +26003,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>17777826000</t>
+          <t>177****6000</t>
         </is>
       </c>
       <c r="E489" t="n">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>17306918759</t>
+          <t>173****8759</t>
         </is>
       </c>
       <c r="E490" t="n">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>13671927686</t>
+          <t>136****7686</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -26081,7 +26081,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E492" t="n">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>13385309523</t>
+          <t>133****9523</t>
         </is>
       </c>
       <c r="E493" t="n">
@@ -26133,7 +26133,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E494" t="n">
@@ -26159,7 +26159,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>15300636118</t>
+          <t>153****6118</t>
         </is>
       </c>
       <c r="E495" t="n">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E496" t="n">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E497" t="n">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E498" t="n">
@@ -26263,7 +26263,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E499" t="n">
@@ -26289,7 +26289,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>13811027270</t>
+          <t>138****7270</t>
         </is>
       </c>
       <c r="E500" t="n">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E501" t="n">
@@ -26341,7 +26341,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E502" t="n">
@@ -26367,7 +26367,7 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>13910771770</t>
+          <t>139****1770</t>
         </is>
       </c>
       <c r="E503" t="n">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E504" t="n">
@@ -26419,7 +26419,7 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>13122359792</t>
+          <t>131****9792</t>
         </is>
       </c>
       <c r="E505" t="n">
@@ -26445,7 +26445,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E506" t="n">
@@ -26471,7 +26471,7 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>13693230356</t>
+          <t>136****0356</t>
         </is>
       </c>
       <c r="E507" t="n">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E508" t="n">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E509" t="n">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>13910135667</t>
+          <t>139****5667</t>
         </is>
       </c>
       <c r="E510" t="n">
@@ -26575,7 +26575,7 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E511" t="n">
@@ -26601,7 +26601,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>13959152114</t>
+          <t>139****2114</t>
         </is>
       </c>
       <c r="E512" t="n">
@@ -26627,7 +26627,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E513" t="n">
@@ -26653,7 +26653,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E514" t="n">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E515" t="n">
@@ -26705,7 +26705,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E516" t="n">
@@ -26731,7 +26731,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E517" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>17701033777</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E518" t="n">
